--- a/artfynd/A 9445-2022 artfynd.xlsx
+++ b/artfynd/A 9445-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 9445-2022 artfynd.xlsx
+++ b/artfynd/A 9445-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -786,6 +786,108 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>124047089</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100257</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Grävlingkärret, Grävlingkärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>674615</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6614220</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Orkesta</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Elin Pöllänen</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Elin Pöllänen</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 9445-2022 artfynd.xlsx
+++ b/artfynd/A 9445-2022 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>99411754</v>
       </c>
       <c r="B2" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -717,10 +712,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>674665.3249865361</v>
+        <v>674665</v>
       </c>
       <c r="R2" t="n">
-        <v>6614126.924258207</v>
+        <v>6614127</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,19 +745,9 @@
           <t>2022-03-24</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-03-24</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,12 +777,7 @@
         <v>124047089</v>
       </c>
       <c r="B3" t="n">
-        <v>100279</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
